--- a/Total War Battleship.xlsx
+++ b/Total War Battleship.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\A\ITEM\UNITY\Total War Battleship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4251A8E0-DA05-4D3D-AD17-2F4FD6C58420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A12ACE8-B451-4AEA-9C03-E2AC98265F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="640" windowWidth="18710" windowHeight="12480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概论" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>做了一个武器系统的脚本，挂在炮塔根节点上。</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,13 +103,125 @@
   <si>
     <t>这套目前用的是默认的，因此有很多冗余操作。后续可以去掉或修改。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">所有的战斗单位（玩家船、敌船、甚至可破坏的礁石）都挂载 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>Damageable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 脚本。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>阵营逻辑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>public bool isEnemy;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：玩家及其队友。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：敌人（风帆战舰）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>作用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">：武器系统扫描到物体时，只需判断 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>if (target.isEnemy != this.isEnemy)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 即可确定是否开火。</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +235,21 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -145,8 +272,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -428,24 +567,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -458,32 +597,75 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D59591-ED35-4453-915E-8FFEFECDFD3A}">
-  <dimension ref="A2:A7"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:A20"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -495,29 +677,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C564F08-D798-4722-B899-71B074EC92DC}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -531,29 +713,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBFD5168-9194-4E99-81D5-5909E541B86F}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>14</v>
       </c>

--- a/Total War Battleship.xlsx
+++ b/Total War Battleship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\A\ITEM\UNITY\Total War Battleship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A12ACE8-B451-4AEA-9C03-E2AC98265F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A60DF4-9105-4BDB-A9FF-B8B2FC2B75B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,26 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>做了一个武器系统的脚本，挂在炮塔根节点上。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器都有一个平行的扇形索敌区域（可设置）。如果区域内有敌人，炮台就会开始瞄准。在瞄准到差不多——一个更小的扇形的时候，就会开始开火。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次开火，会有一个冷却时间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器有个简单的状态机，用来实现待机，旋转瞄准，开火</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器是自动开火的。一艘船可以搭载若干个武器。</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>使用CinemachineCamera</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -105,14 +86,135 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">所有的战斗单位（玩家船、敌船、甚至可破坏的礁石）都挂载 </t>
+    <t>1. 系统概述</t>
+  </si>
+  <si>
+    <t>本系统采用**“高度解耦、原子化组件”**的设计架构。将传统的火控系统拆分为“指向器（Turret）”与“发射器（Weapon）”两个独立单元，由“核心（UnitCore）”进行统一调度。这种设计支持多种作战单位（如战舰主炮、侧舷固定炮、岸防炮等）的灵活组装，无需修改底层代码。</t>
+  </si>
+  <si>
+    <t>2. 核心组件定义</t>
+  </si>
+  <si>
+    <t>2.1 UnitCore (单位核心)</t>
+  </si>
+  <si>
+    <r>
+      <t>职能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：作为单位的“总装配器”和阵营管理器。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>阵营逻辑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：持有 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>isEnemy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 布尔值（False 为玩家/友军，True 为敌军）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>初始化机制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 生命周期内，一次性获取所有子物体中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Turret</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 与 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Weapon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 零件，并将对应的敌人 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
         <family val="2"/>
       </rPr>
       <t>Damageable</t>
@@ -121,99 +223,507 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 脚本。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>阵营逻辑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 列表引用及阵营信息分发给它们。</t>
+    </r>
+  </si>
+  <si>
+    <t>2.2 Turret (自动指向器)</t>
+  </si>
+  <si>
+    <r>
+      <t>职能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：独立的物理追踪单元，充当“瞄准架”角色。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>索敌逻辑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>maxRange</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 半径内通过缓存的敌人列表寻找最近目标。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>旋转机制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：驱动 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>gunNode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 在水平方向（XY平面）顺滑转向目标，支持自定义旋转速度。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>解耦特性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：不负责开火，不感知 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Weapon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 的存在，仅执行指向动作。</t>
+    </r>
+  </si>
+  <si>
+    <t>2.3 Weapon (原子发射器)</t>
+  </si>
+  <si>
+    <r>
+      <t>职能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：独立的火力执行单元，挂载于炮管或固定炮位。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>发射机制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：自身即为炮口（Fire Point），直接取当前坐标与朝向进行实例化。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>判定逻辑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>：</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>沙漏冷却</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：基于 </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>public bool isEnemy;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：玩家及其队友。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：敌人（风帆战舰）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>作用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">：武器系统扫描到物体时，只需判断 </t>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Time.deltaTime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 的倒计时计时器，天然适配游戏暂停与倍速逻辑。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>对齐开火</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：独立判定自身正前方（Forward）在水平面上与目标的夹角是否小于 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>if (target.isEnemy != this.isEnemy)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 即可确定是否开火。</t>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>fireThreshold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>，满足条件则自动开火。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>接口支持</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：支持 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>isAuto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 自主模式，同时暴露 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>TryFire()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 接口供外部（如玩家手动齐射）调用。</t>
+    </r>
+  </si>
+  <si>
+    <t>3. 战斗逻辑与阵营规则</t>
+  </si>
+  <si>
+    <r>
+      <t>Damageable 体系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：所有可破坏物体（船只、礁石、建筑）必须挂载 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Damageable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 脚本并注册至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>BattleSceneController</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>阵营判定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：零件通过 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>targetList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 进行识别。若自身阵营与目标列表匹配，则视为合法攻击对象。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>物理级解耦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>：当炮塔转动对齐目标时，武器因物理朝向一致自动触发开火。若目标移动过快导致炮塔未对齐，武器将自动停火，无需状态机干预。</t>
+    </r>
+  </si>
+  <si>
+    <t>4. 应用场景示例</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>配置方案</t>
+  </si>
+  <si>
+    <t>行为表现</t>
+  </si>
+  <si>
+    <t>主旋转炮塔</t>
+  </si>
+  <si>
+    <t>炮塔转动寻敌，对齐后武器自动/受控开火。</t>
+  </si>
+  <si>
+    <t>侧舷固定炮</t>
+  </si>
+  <si>
+    <t>不旋转，仅攻击进入船只侧方扇形区域的敌人。</t>
+  </si>
+  <si>
+    <t>岸防/水雷</t>
+  </si>
+  <si>
+    <t>作为独立零件放置，自动防御进入范围的敌方单位。</t>
+  </si>
+  <si>
+    <r>
+      <t>Turret</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Weapon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">仅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Weapon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (开启 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>isAuto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Weapon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>UnitCore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 手动赋值)</t>
     </r>
   </si>
 </sst>
@@ -221,7 +731,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,18 +748,62 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial Unicode MS"/>
+      <name val="Google Sans Text"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -260,7 +814,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -268,23 +822,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -571,22 +1165,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -597,76 +1191,233 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D59591-ED35-4453-915E-8FFEFECDFD3A}">
-  <dimension ref="A2:A20"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>0</v>
+    <row r="1" spans="1:1" ht="23">
+      <c r="A1" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>3</v>
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="23">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="17.5">
+      <c r="A7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" t="s">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1"/>
-    </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1"/>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="3"/>
+    <row r="15" spans="1:1" ht="17.5">
+      <c r="A15" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="A16" s="1"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="3"/>
+      <c r="A17" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="A18" s="1"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="1"/>
+      <c r="A19" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="17.5">
+      <c r="A25" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="23">
+      <c r="A40" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="23">
+      <c r="A48" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.5" thickBot="1"/>
+    <row r="50" spans="1:6" ht="14.5" thickBot="1">
+      <c r="A50" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="14.5" thickBot="1">
+      <c r="A51" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="1:6" ht="14.5" thickBot="1">
+      <c r="A52" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:6" ht="14.5" thickBot="1">
+      <c r="A53" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -681,27 +1432,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -717,27 +1468,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Total War Battleship.xlsx
+++ b/Total War Battleship.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\A\ITEM\UNITY\Total War Battleship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A60DF4-9105-4BDB-A9FF-B8B2FC2B75B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3FC4B1-A66F-4838-8A87-A3B7206143DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="战斗" sheetId="2" r:id="rId2"/>
     <sheet name="镜头" sheetId="3" r:id="rId3"/>
     <sheet name="移动" sheetId="4" r:id="rId4"/>
+    <sheet name="计划" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>使用CinemachineCamera</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -725,13 +726,45 @@
       </rPr>
       <t xml:space="preserve"> 手动赋值)</t>
     </r>
+  </si>
+  <si>
+    <t>开始界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼雷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水雷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>准备增加鱼雷。基于目前的炮弹系统进行修改。不会自动发射，由玩家手动点击按钮操作。冷却时间长。鱼雷移动速度比所有船稍快，威力大。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水雷：由敌方发射，可长时间存在于场景中，不会移动，只会伤害玩家，但会被友方消除（无伤害）。发射冷却较长。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -805,6 +838,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -841,7 +886,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -878,6 +923,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1191,7 +1239,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D59591-ED35-4453-915E-8FFEFECDFD3A}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:1" ht="23">
@@ -1418,6 +1466,16 @@
         <v>46</v>
       </c>
       <c r="F53" s="12"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.5">
+      <c r="A56" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1495,4 +1553,36 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC1C3BB5-1300-4669-B95F-2709372CE8CA}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="B2:C4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>